--- a/artfynd/A 2938-2025 artfynd.xlsx
+++ b/artfynd/A 2938-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122652731</v>
       </c>
       <c r="B2" t="n">
-        <v>82443</v>
+        <v>82444</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>122652714</v>
       </c>
       <c r="B3" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 2938-2025 artfynd.xlsx
+++ b/artfynd/A 2938-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122652731</v>
       </c>
       <c r="B2" t="n">
-        <v>82444</v>
+        <v>82447</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 2938-2025 artfynd.xlsx
+++ b/artfynd/A 2938-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122652731</v>
+        <v>122652714</v>
       </c>
       <c r="B2" t="n">
-        <v>82447</v>
+        <v>57384</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>407270</v>
+        <v>407189</v>
       </c>
       <c r="R2" t="n">
-        <v>6689007</v>
+        <v>6688924</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,7 +767,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122652714</v>
+        <v>122652731</v>
       </c>
       <c r="B3" t="n">
-        <v>57384</v>
+        <v>82447</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,31 +801,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>407189</v>
+        <v>407270</v>
       </c>
       <c r="R3" t="n">
-        <v>6688924</v>
+        <v>6689007</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,6 +872,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 2938-2025 artfynd.xlsx
+++ b/artfynd/A 2938-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122652731</v>
+        <v>122652714</v>
       </c>
       <c r="B2" t="n">
-        <v>82549</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>407270</v>
+        <v>407189</v>
       </c>
       <c r="R2" t="n">
-        <v>6689007</v>
+        <v>6688924</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,7 +767,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122652714</v>
+        <v>122652731</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>82553</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,31 +801,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>407189</v>
+        <v>407270</v>
       </c>
       <c r="R3" t="n">
-        <v>6688924</v>
+        <v>6689007</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,6 +872,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 2938-2025 artfynd.xlsx
+++ b/artfynd/A 2938-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122652714</v>
+        <v>122652731</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>82553</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>407189</v>
+        <v>407270</v>
       </c>
       <c r="R2" t="n">
-        <v>6688924</v>
+        <v>6689007</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -767,6 +762,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122652731</v>
+        <v>122652714</v>
       </c>
       <c r="B3" t="n">
-        <v>82553</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,26 +797,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -828,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>407270</v>
+        <v>407189</v>
       </c>
       <c r="R3" t="n">
-        <v>6689007</v>
+        <v>6688924</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +873,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 2938-2025 artfynd.xlsx
+++ b/artfynd/A 2938-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122652731</v>
+        <v>122652714</v>
       </c>
       <c r="B2" t="n">
-        <v>82553</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>407270</v>
+        <v>407189</v>
       </c>
       <c r="R2" t="n">
-        <v>6689007</v>
+        <v>6688924</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,7 +767,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122652714</v>
+        <v>122652731</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>82553</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,31 +801,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>407189</v>
+        <v>407270</v>
       </c>
       <c r="R3" t="n">
-        <v>6688924</v>
+        <v>6689007</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,6 +872,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 2938-2025 artfynd.xlsx
+++ b/artfynd/A 2938-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -889,6 +889,536 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123440828</v>
+      </c>
+      <c r="B4" t="n">
+        <v>78771</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Skarpmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>407329</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6689057</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Malin Henell</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Malin Henell, Rosanne Håkansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123440799</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78771</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skarpmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>407220</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6689012</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Malin Henell</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Malin Henell, Rosanne Håkansson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123440874</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57634</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skarpmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>407380</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6689153</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Malin Henell</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Malin Henell, Rosanne Håkansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123440731</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78771</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skarpmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>407208</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6688935</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Malin Henell</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Malin Henell, Rosanne Håkansson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123440820</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78771</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skarpmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>407284</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6689010</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Malin Henell</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Malin Henell, Rosanne Håkansson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2938-2025 artfynd.xlsx
+++ b/artfynd/A 2938-2025 artfynd.xlsx
@@ -891,7 +891,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123440828</v>
+        <v>123440799</v>
       </c>
       <c r="B4" t="n">
         <v>78771</v>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>407329</v>
+        <v>407220</v>
       </c>
       <c r="R4" t="n">
-        <v>6689057</v>
+        <v>6689012</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -997,7 +997,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123440799</v>
+        <v>123440731</v>
       </c>
       <c r="B5" t="n">
         <v>78771</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>407220</v>
+        <v>407208</v>
       </c>
       <c r="R5" t="n">
-        <v>6689012</v>
+        <v>6688935</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123440874</v>
+        <v>123440828</v>
       </c>
       <c r="B6" t="n">
-        <v>57634</v>
+        <v>78771</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,27 +1119,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1147,13 +1146,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>407380</v>
+        <v>407329</v>
       </c>
       <c r="R6" t="n">
-        <v>6689153</v>
+        <v>6689057</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1191,6 +1190,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1209,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123440731</v>
+        <v>123440874</v>
       </c>
       <c r="B7" t="n">
-        <v>78771</v>
+        <v>57634</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,26 +1225,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1252,13 +1253,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>407208</v>
+        <v>407380</v>
       </c>
       <c r="R7" t="n">
-        <v>6688935</v>
+        <v>6689153</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1296,7 +1297,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 2938-2025 artfynd.xlsx
+++ b/artfynd/A 2938-2025 artfynd.xlsx
@@ -891,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123440799</v>
+        <v>123440828</v>
       </c>
       <c r="B4" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>407220</v>
+        <v>407329</v>
       </c>
       <c r="R4" t="n">
-        <v>6689012</v>
+        <v>6689057</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -990,17 +990,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Malin Henell, Rosanne Håkansson</t>
+          <t>Rosanne Håkansson, Malin Henell</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123440731</v>
+        <v>123440799</v>
       </c>
       <c r="B5" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>407208</v>
+        <v>407220</v>
       </c>
       <c r="R5" t="n">
-        <v>6688935</v>
+        <v>6689012</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1096,17 +1096,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Malin Henell, Rosanne Håkansson</t>
+          <t>Rosanne Håkansson, Malin Henell</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123440828</v>
+        <v>123440820</v>
       </c>
       <c r="B6" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>407329</v>
+        <v>407284</v>
       </c>
       <c r="R6" t="n">
-        <v>6689057</v>
+        <v>6689010</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Malin Henell, Rosanne Håkansson</t>
+          <t>Rosanne Håkansson, Malin Henell</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1315,10 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123440820</v>
+        <v>123440731</v>
       </c>
       <c r="B8" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1358,10 +1358,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>407284</v>
+        <v>407208</v>
       </c>
       <c r="R8" t="n">
-        <v>6689010</v>
+        <v>6688935</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>

--- a/artfynd/A 2938-2025 artfynd.xlsx
+++ b/artfynd/A 2938-2025 artfynd.xlsx
@@ -891,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123440828</v>
+        <v>123440799</v>
       </c>
       <c r="B4" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>407329</v>
+        <v>407220</v>
       </c>
       <c r="R4" t="n">
-        <v>6689057</v>
+        <v>6689012</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -997,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123440799</v>
+        <v>123440731</v>
       </c>
       <c r="B5" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>407220</v>
+        <v>407208</v>
       </c>
       <c r="R5" t="n">
-        <v>6689012</v>
+        <v>6688935</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1106,7 +1106,7 @@
         <v>123440874</v>
       </c>
       <c r="B6" t="n">
-        <v>57634</v>
+        <v>57640</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1209,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123440731</v>
+        <v>123440828</v>
       </c>
       <c r="B7" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>407208</v>
+        <v>407329</v>
       </c>
       <c r="R7" t="n">
-        <v>6688935</v>
+        <v>6689057</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1318,7 +1318,7 @@
         <v>123440820</v>
       </c>
       <c r="B8" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 2938-2025 artfynd.xlsx
+++ b/artfynd/A 2938-2025 artfynd.xlsx
@@ -891,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123440799</v>
+        <v>123440828</v>
       </c>
       <c r="B4" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>407220</v>
+        <v>407329</v>
       </c>
       <c r="R4" t="n">
-        <v>6689012</v>
+        <v>6689057</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1000,7 +1000,7 @@
         <v>123440731</v>
       </c>
       <c r="B5" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>123440874</v>
       </c>
       <c r="B6" t="n">
-        <v>57640</v>
+        <v>57643</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1209,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123440828</v>
+        <v>123440820</v>
       </c>
       <c r="B7" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>407329</v>
+        <v>407284</v>
       </c>
       <c r="R7" t="n">
-        <v>6689057</v>
+        <v>6689010</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1315,10 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123440820</v>
+        <v>123440799</v>
       </c>
       <c r="B8" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1358,10 +1358,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>407284</v>
+        <v>407220</v>
       </c>
       <c r="R8" t="n">
-        <v>6689010</v>
+        <v>6689012</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>

--- a/artfynd/A 2938-2025 artfynd.xlsx
+++ b/artfynd/A 2938-2025 artfynd.xlsx
@@ -891,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123440828</v>
+        <v>123440799</v>
       </c>
       <c r="B4" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>407329</v>
+        <v>407220</v>
       </c>
       <c r="R4" t="n">
-        <v>6689057</v>
+        <v>6689012</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1000,7 +1000,7 @@
         <v>123440731</v>
       </c>
       <c r="B5" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123440874</v>
+        <v>123440820</v>
       </c>
       <c r="B6" t="n">
-        <v>57643</v>
+        <v>78788</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,27 +1119,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1147,13 +1146,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>407380</v>
+        <v>407284</v>
       </c>
       <c r="R6" t="n">
-        <v>6689153</v>
+        <v>6689010</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1191,6 +1190,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1209,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123440820</v>
+        <v>123440874</v>
       </c>
       <c r="B7" t="n">
-        <v>78786</v>
+        <v>57644</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,26 +1225,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1252,13 +1253,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>407284</v>
+        <v>407380</v>
       </c>
       <c r="R7" t="n">
-        <v>6689010</v>
+        <v>6689153</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1296,7 +1297,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1315,10 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123440799</v>
+        <v>123440828</v>
       </c>
       <c r="B8" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1358,10 +1358,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>407220</v>
+        <v>407329</v>
       </c>
       <c r="R8" t="n">
-        <v>6689012</v>
+        <v>6689057</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>

--- a/artfynd/A 2938-2025 artfynd.xlsx
+++ b/artfynd/A 2938-2025 artfynd.xlsx
@@ -891,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123440799</v>
+        <v>123440874</v>
       </c>
       <c r="B4" t="n">
-        <v>78788</v>
+        <v>57644</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,26 +907,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -934,13 +935,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>407220</v>
+        <v>407380</v>
       </c>
       <c r="R4" t="n">
-        <v>6689012</v>
+        <v>6689153</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,7 +979,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1209,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123440874</v>
+        <v>123440799</v>
       </c>
       <c r="B7" t="n">
-        <v>57644</v>
+        <v>78788</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,27 +1225,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1253,13 +1252,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>407380</v>
+        <v>407220</v>
       </c>
       <c r="R7" t="n">
-        <v>6689153</v>
+        <v>6689012</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1297,6 +1296,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 2938-2025 artfynd.xlsx
+++ b/artfynd/A 2938-2025 artfynd.xlsx
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123440820</v>
+        <v>123440799</v>
       </c>
       <c r="B6" t="n">
         <v>78788</v>
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>407284</v>
+        <v>407220</v>
       </c>
       <c r="R6" t="n">
-        <v>6689010</v>
+        <v>6689012</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1209,7 +1209,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123440799</v>
+        <v>123440820</v>
       </c>
       <c r="B7" t="n">
         <v>78788</v>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>407220</v>
+        <v>407284</v>
       </c>
       <c r="R7" t="n">
-        <v>6689012</v>
+        <v>6689010</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>

--- a/artfynd/A 2938-2025 artfynd.xlsx
+++ b/artfynd/A 2938-2025 artfynd.xlsx
@@ -891,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123440874</v>
+        <v>123440820</v>
       </c>
       <c r="B4" t="n">
-        <v>57644</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,27 +907,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -935,13 +934,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>407380</v>
+        <v>407284</v>
       </c>
       <c r="R4" t="n">
-        <v>6689153</v>
+        <v>6689010</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,6 +978,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -997,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123440731</v>
+        <v>123440874</v>
       </c>
       <c r="B5" t="n">
-        <v>78788</v>
+        <v>57644</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,26 +1013,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1040,13 +1041,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>407208</v>
+        <v>407380</v>
       </c>
       <c r="R5" t="n">
-        <v>6688935</v>
+        <v>6689153</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,7 +1085,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123440799</v>
+        <v>123440731</v>
       </c>
       <c r="B6" t="n">
         <v>78788</v>
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>407220</v>
+        <v>407208</v>
       </c>
       <c r="R6" t="n">
-        <v>6689012</v>
+        <v>6688935</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1209,7 +1209,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123440820</v>
+        <v>123440828</v>
       </c>
       <c r="B7" t="n">
         <v>78788</v>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>407284</v>
+        <v>407329</v>
       </c>
       <c r="R7" t="n">
-        <v>6689010</v>
+        <v>6689057</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1315,7 +1315,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123440828</v>
+        <v>123440799</v>
       </c>
       <c r="B8" t="n">
         <v>78788</v>
@@ -1358,10 +1358,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>407329</v>
+        <v>407220</v>
       </c>
       <c r="R8" t="n">
-        <v>6689057</v>
+        <v>6689012</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>

--- a/artfynd/A 2938-2025 artfynd.xlsx
+++ b/artfynd/A 2938-2025 artfynd.xlsx
@@ -891,7 +891,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123440820</v>
+        <v>123440828</v>
       </c>
       <c r="B4" t="n">
         <v>78788</v>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>407284</v>
+        <v>407329</v>
       </c>
       <c r="R4" t="n">
-        <v>6689010</v>
+        <v>6689057</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123440731</v>
+        <v>123440820</v>
       </c>
       <c r="B6" t="n">
         <v>78788</v>
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>407208</v>
+        <v>407284</v>
       </c>
       <c r="R6" t="n">
-        <v>6688935</v>
+        <v>6689010</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1209,7 +1209,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123440828</v>
+        <v>123440731</v>
       </c>
       <c r="B7" t="n">
         <v>78788</v>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>407329</v>
+        <v>407208</v>
       </c>
       <c r="R7" t="n">
-        <v>6689057</v>
+        <v>6688935</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>

--- a/artfynd/A 2938-2025 artfynd.xlsx
+++ b/artfynd/A 2938-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122652714</v>
+        <v>122652731</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,31 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>407189</v>
+        <v>407270</v>
       </c>
       <c r="R2" t="n">
-        <v>6688924</v>
+        <v>6689007</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -767,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122652731</v>
+        <v>123440731</v>
       </c>
       <c r="B3" t="n">
-        <v>82553</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -828,13 +814,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>407270</v>
+        <v>407208</v>
       </c>
       <c r="R3" t="n">
-        <v>6689007</v>
+        <v>6688935</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +865,7 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Rosanne Håkansson</t>
+          <t>Malin Henell</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -891,19 +877,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123440731</v>
+        <v>123440799</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -934,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>407208</v>
+        <v>407220</v>
       </c>
       <c r="R4" t="n">
-        <v>6688935</v>
+        <v>6689012</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -990,7 +971,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Rosanne Håkansson, Malin Henell</t>
+          <t>Malin Henell, Rosanne Håkansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1000,16 +981,11 @@
         <v>123440820</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1103,19 +1079,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123440799</v>
+        <v>123440828</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1146,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>407220</v>
+        <v>407329</v>
       </c>
       <c r="R6" t="n">
-        <v>6689012</v>
+        <v>6689057</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1209,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123440828</v>
+        <v>122652690</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1225,26 +1191,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1252,13 +1223,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>407329</v>
+        <v>407200</v>
       </c>
       <c r="R7" t="n">
-        <v>6689057</v>
+        <v>6689033</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1296,34 +1267,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Malin Henell</t>
+          <t>Rosanne Håkansson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Malin Henell, Rosanne Håkansson</t>
+          <t>Rosanne Håkansson, Malin Henell</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123440874</v>
+        <v>122652714</v>
       </c>
       <c r="B8" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1331,27 +1296,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1359,10 +1328,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>407380</v>
+        <v>407189</v>
       </c>
       <c r="R8" t="n">
-        <v>6689153</v>
+        <v>6688924</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,15 +1378,116 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>Rosanne Håkansson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Rosanne Håkansson, Malin Henell</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123440874</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Skarpmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>407380</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6689153</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>Malin Henell</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>Malin Henell, Rosanne Håkansson</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2938-2025 artfynd.xlsx
+++ b/artfynd/A 2938-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122652731</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123440731</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123440799</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123440820</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123440828</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1282,6 +1312,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122652690</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1387,6 +1422,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122652714</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,8 +1528,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123440874</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>